--- a/output/pdf_financials_xlsx/LGC.xlsx
+++ b/output/pdf_financials_xlsx/LGC.xlsx
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.048928</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.020082</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.021892</v>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.465016</v>
+        <v>0.416088</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.315482</v>
+        <v>0.2954</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.865054</v>
+        <v>0.843162</v>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
@@ -4033,7 +4033,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -4997,7 +5001,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6008,7 +6016,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LGC.xlsx
+++ b/output/pdf_financials_xlsx/LGC.xlsx
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.042498</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.150007</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.355739</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.24894</v>
       </c>
     </row>
     <row r="13">
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.931684</v>
+        <v>-1.889186</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.037228</v>
+        <v>-2.187235</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.668107</v>
+        <v>-4.023846</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.675908</v>
+        <v>-3.924848</v>
       </c>
     </row>
     <row r="28">
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.907559</v>
+        <v>-1.865061</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.005053</v>
+        <v>-2.15506</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.635084</v>
+        <v>-3.990823</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.675908</v>
+        <v>-3.924848</v>
       </c>
     </row>
     <row r="30">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">

--- a/output/pdf_financials_xlsx/LGC.xlsx
+++ b/output/pdf_financials_xlsx/LGC.xlsx
@@ -1099,7 +1099,7 @@
         <v>0.033023</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.032172</v>
       </c>
     </row>
     <row r="29">
@@ -1123,7 +1123,7 @@
         <v>-3.990823</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.924848</v>
+        <v>-3.892676</v>
       </c>
     </row>
     <row r="30">
@@ -1241,10 +1241,8 @@
       <c r="E34" s="3" t="n">
         <v>1.649592</v>
       </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1267,10 +1265,8 @@
       <c r="E35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1293,10 +1289,8 @@
       <c r="E36" s="3" t="n">
         <v>1.649592</v>
       </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1319,10 +1313,8 @@
       <c r="E37" s="3" t="n">
         <v>0.027782</v>
       </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="3" t="n">
+        <v>0.040853</v>
       </c>
     </row>
     <row r="38">
@@ -1345,10 +1337,8 @@
       <c r="E38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1371,10 +1361,8 @@
       <c r="E39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1397,10 +1385,8 @@
       <c r="E40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1423,10 +1409,8 @@
       <c r="E41" s="3" t="n">
         <v>0.027782</v>
       </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F41" s="3" t="n">
+        <v>0.040853</v>
       </c>
     </row>
     <row r="42">
@@ -1449,10 +1433,8 @@
       <c r="E42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1475,10 +1457,8 @@
       <c r="E43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1501,10 +1481,8 @@
       <c r="E44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1527,10 +1505,8 @@
       <c r="E45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1553,10 +1529,8 @@
       <c r="E46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1579,10 +1553,8 @@
       <c r="E47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1605,10 +1577,8 @@
       <c r="E48" s="3" t="n">
         <v>0.090902</v>
       </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" s="3" t="n">
+        <v>4.549436</v>
       </c>
     </row>
     <row r="49">
@@ -1631,10 +1601,8 @@
       <c r="E49" s="3" t="n">
         <v>1.768276</v>
       </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="3" t="n">
+        <v>4.590289</v>
       </c>
     </row>
     <row r="50">
@@ -1657,10 +1625,8 @@
       <c r="E50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1683,10 +1649,8 @@
       <c r="E51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1709,10 +1673,8 @@
       <c r="E52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1735,10 +1697,8 @@
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1761,10 +1721,8 @@
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1819,10 +1777,8 @@
       <c r="E56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1845,10 +1801,8 @@
       <c r="E57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1871,10 +1825,8 @@
       <c r="E58" s="3" t="n">
         <v>0.288774</v>
       </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="3" t="n">
+        <v>0.184056</v>
       </c>
     </row>
     <row r="59">
@@ -1897,10 +1849,8 @@
       <c r="E59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1923,10 +1873,8 @@
       <c r="E60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1949,10 +1897,8 @@
       <c r="E61" s="3" t="n">
         <v>23.883422</v>
       </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="3" t="n">
+        <v>32.697072</v>
       </c>
     </row>
     <row r="62">
@@ -1975,10 +1921,8 @@
       <c r="E62" s="3" t="n">
         <v>24.172196</v>
       </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="3" t="n">
+        <v>32.881128</v>
       </c>
     </row>
     <row r="63">
@@ -2001,10 +1945,8 @@
       <c r="E63" s="3" t="n">
         <v>25.940472</v>
       </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="3" t="n">
+        <v>37.471417</v>
       </c>
     </row>
     <row r="64">
@@ -2027,10 +1969,8 @@
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2053,10 +1993,8 @@
       <c r="E65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2079,10 +2017,8 @@
       <c r="E66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2105,10 +2041,8 @@
       <c r="E67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2131,10 +2065,8 @@
       <c r="E68" s="3" t="n">
         <v>1.109909</v>
       </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" s="3" t="n">
+        <v>1.323633</v>
       </c>
     </row>
     <row r="69">
@@ -2157,10 +2089,8 @@
       <c r="E69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2183,10 +2113,8 @@
       <c r="E70" s="3" t="n">
         <v>0.060443</v>
       </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="3" t="n">
+        <v>0.07204199999999999</v>
       </c>
     </row>
     <row r="71">
@@ -2209,10 +2137,8 @@
       <c r="E71" s="3" t="n">
         <v>0.060443</v>
       </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" s="3" t="n">
+        <v>0.07204199999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2235,10 +2161,8 @@
       <c r="E72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2261,10 +2185,8 @@
       <c r="E73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2287,10 +2209,8 @@
       <c r="E74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2313,10 +2233,8 @@
       <c r="E75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2339,10 +2257,8 @@
       <c r="E76" s="3" t="n">
         <v>1.170352</v>
       </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="3" t="n">
+        <v>1.395675</v>
       </c>
     </row>
     <row r="77">
@@ -2365,10 +2281,8 @@
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2391,10 +2305,8 @@
       <c r="E78" s="3" t="n">
         <v>0.102637</v>
       </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="3" t="n">
+        <v>0.043342</v>
       </c>
     </row>
     <row r="79">
@@ -2417,10 +2329,8 @@
       <c r="E79" s="3" t="n">
         <v>0.102637</v>
       </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" s="3" t="n">
+        <v>0.043342</v>
       </c>
     </row>
     <row r="80">
@@ -2443,10 +2353,8 @@
       <c r="E80" s="3" t="n">
         <v>0.006611132558599513</v>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>0.003202229104916686</v>
       </c>
     </row>
     <row r="81">
@@ -2469,10 +2377,8 @@
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2495,10 +2401,8 @@
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2521,10 +2425,8 @@
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2547,10 +2449,8 @@
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2573,10 +2473,8 @@
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2599,10 +2497,8 @@
       <c r="E86" s="3" t="n">
         <v>0.102637</v>
       </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F86" s="3" t="n">
+        <v>0.043342</v>
       </c>
     </row>
     <row r="87">
@@ -2625,10 +2521,8 @@
       <c r="E87" s="3" t="n">
         <v>1.272989</v>
       </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="3" t="n">
+        <v>1.439017</v>
       </c>
     </row>
     <row r="88">
@@ -2651,10 +2545,8 @@
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2677,10 +2569,8 @@
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2703,10 +2593,8 @@
       <c r="E90" s="3" t="n">
         <v>-7.637019</v>
       </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" s="3" t="n">
+        <v>-11.312927</v>
       </c>
     </row>
     <row r="91">
@@ -2729,10 +2617,8 @@
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2755,10 +2641,8 @@
       <c r="E92" s="3" t="n">
         <v>2.416743</v>
       </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="3" t="n">
+        <v>3.171079</v>
       </c>
     </row>
     <row r="93">
@@ -2781,10 +2665,8 @@
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2807,10 +2689,8 @@
       <c r="E94" s="3" t="n">
         <v>24.667483</v>
       </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" s="3" t="n">
+        <v>36.0324</v>
       </c>
     </row>
     <row r="95">
@@ -2833,10 +2713,8 @@
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2859,10 +2737,8 @@
       <c r="E96" s="3" t="n">
         <v>24.667483</v>
       </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F96" s="3" t="n">
+        <v>36.0324</v>
       </c>
     </row>
     <row r="97">
@@ -2885,10 +2761,8 @@
       <c r="E97" s="3" t="n">
         <v>0.9509265290161258</v>
       </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="3" t="n">
+        <v>0.9615969420104929</v>
       </c>
     </row>
     <row r="98">
@@ -2918,10 +2792,8 @@
       <c r="E99" s="3" t="n">
         <v>-3.668107</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-3.675908</v>
       </c>
     </row>
     <row r="100">
@@ -2944,10 +2816,8 @@
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2970,10 +2840,8 @@
       <c r="E101" s="3" t="n">
         <v>0.003133</v>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>-0.013071</v>
       </c>
     </row>
     <row r="102">
@@ -2996,10 +2864,8 @@
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3022,10 +2888,8 @@
       <c r="E103" s="3" t="n">
         <v>-0.021892</v>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>-0.255684</v>
       </c>
     </row>
     <row r="104">
@@ -3048,10 +2912,8 @@
       <c r="E104" s="3" t="n">
         <v>0.861921</v>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>1.003589</v>
       </c>
     </row>
     <row r="105">
@@ -3074,10 +2936,8 @@
       <c r="E105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3100,10 +2960,8 @@
       <c r="E106" s="3" t="n">
         <v>0.843162</v>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>0.734834</v>
       </c>
     </row>
     <row r="107">
@@ -3126,10 +2984,8 @@
       <c r="E107" s="3" t="n">
         <v>1.450556</v>
       </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="3" t="n">
+        <v>0.8532920000000001</v>
       </c>
     </row>
     <row r="108">
@@ -3152,10 +3008,8 @@
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3178,10 +3032,8 @@
       <c r="E109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3204,10 +3056,8 @@
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3230,10 +3080,8 @@
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3256,10 +3104,8 @@
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3282,10 +3128,8 @@
       <c r="E113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3308,10 +3152,8 @@
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3334,10 +3176,8 @@
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3360,10 +3200,8 @@
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3386,10 +3224,8 @@
       <c r="E117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3412,10 +3248,8 @@
       <c r="E118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3438,10 +3272,8 @@
       <c r="E119" s="3" t="n">
         <v>-7.190062</v>
       </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F119" s="3" t="n">
+        <v>-8.351086</v>
       </c>
     </row>
     <row r="120">
@@ -3464,10 +3296,8 @@
       <c r="E120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3490,10 +3320,8 @@
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3516,10 +3344,8 @@
       <c r="E122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3542,10 +3368,8 @@
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3568,10 +3392,8 @@
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3594,10 +3416,8 @@
       <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3620,10 +3440,8 @@
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3678,10 +3496,8 @@
       <c r="E128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3704,10 +3520,8 @@
       <c r="E129" s="3" t="n">
         <v>-0.069656</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>13.957351</v>
       </c>
     </row>
     <row r="130">
@@ -3730,10 +3544,8 @@
       <c r="E130" s="3" t="n">
         <v>11.052838</v>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="3" t="n">
+        <v>1.649592</v>
       </c>
     </row>
     <row r="131">
@@ -3756,10 +3568,8 @@
       <c r="E131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3782,10 +3592,8 @@
       <c r="E132" s="3" t="n">
         <v>-9.403245999999999</v>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>2.553258</v>
       </c>
     </row>
     <row r="133">
@@ -3808,10 +3616,8 @@
       <c r="E133" s="3" t="n">
         <v>1.649592</v>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>4.20285</v>
       </c>
     </row>
     <row r="134">
@@ -3834,10 +3640,8 @@
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3858,12 +3662,10 @@
         <v>-1.728961</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.143528</v>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.196825</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-2.755764</v>
       </c>
     </row>
   </sheetData>
@@ -3877,7 +3679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3946,14 +3748,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 3(e)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>Cash 3(e)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3964,16 +3762,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>11.052838</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H2" s="5" t="n">
         <v>1.649592</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="5" t="n">
+        <v>4.20285</v>
       </c>
     </row>
     <row r="3">
@@ -4011,10 +3809,8 @@
       <c r="H3" s="5" t="n">
         <v>0.027782</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="5" t="n">
+        <v>0.040853</v>
       </c>
     </row>
     <row r="4">
@@ -4052,10 +3848,8 @@
       <c r="H4" s="5" t="n">
         <v>0.090902</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="5" t="n">
+        <v>0.346586</v>
       </c>
     </row>
     <row r="5">
@@ -4093,10 +3887,8 @@
       <c r="H5" s="5" t="n">
         <v>1.768276</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="5" t="n">
+        <v>4.590289</v>
       </c>
     </row>
     <row r="6">
@@ -4130,10 +3922,8 @@
       <c r="H6" s="5" t="n">
         <v>23.883422</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="5" t="n">
+        <v>32.697072</v>
       </c>
     </row>
     <row r="7">
@@ -4171,10 +3961,8 @@
       <c r="H7" s="5" t="n">
         <v>0.288774</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="5" t="n">
+        <v>0.184056</v>
       </c>
     </row>
     <row r="8">
@@ -4212,10 +4000,8 @@
       <c r="H8" s="5" t="n">
         <v>24.172196</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="5" t="n">
+        <v>32.881128</v>
       </c>
     </row>
     <row r="9">
@@ -4253,10 +4039,8 @@
       <c r="H9" s="5" t="n">
         <v>25.940472</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="5" t="n">
+        <v>37.471417</v>
       </c>
     </row>
     <row r="10">
@@ -4294,10 +4078,8 @@
       <c r="H10" s="5" t="n">
         <v>1.109909</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="5" t="n">
+        <v>1.323633</v>
       </c>
     </row>
     <row r="11">
@@ -4335,10 +4117,8 @@
       <c r="H11" s="5" t="n">
         <v>0.060443</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="5" t="n">
+        <v>0.07204199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4376,10 +4156,8 @@
       <c r="H12" s="5" t="n">
         <v>1.170352</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="5" t="n">
+        <v>1.395675</v>
       </c>
     </row>
     <row r="13">
@@ -4417,10 +4195,8 @@
       <c r="H13" s="5" t="n">
         <v>0.102637</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="5" t="n">
+        <v>0.043342</v>
       </c>
     </row>
     <row r="14">
@@ -4458,10 +4234,8 @@
       <c r="H14" s="5" t="n">
         <v>1.272989</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="5" t="n">
+        <v>1.439017</v>
       </c>
     </row>
     <row r="15">
@@ -4491,10 +4265,8 @@
       <c r="H15" s="5" t="n">
         <v>29.887759</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="5" t="n">
+        <v>44.174248</v>
       </c>
     </row>
     <row r="16">
@@ -4528,10 +4300,8 @@
       <c r="H16" s="5" t="n">
         <v>2.416743</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="5" t="n">
+        <v>3.171079</v>
       </c>
     </row>
     <row r="17">
@@ -4565,10 +4335,8 @@
       <c r="H17" s="5" t="n">
         <v>-7.637019</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="5" t="n">
+        <v>-11.312927</v>
       </c>
     </row>
     <row r="18">
@@ -4606,10 +4374,8 @@
       <c r="H18" s="5" t="n">
         <v>24.667483</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="5" t="n">
+        <v>36.0324</v>
       </c>
     </row>
     <row r="19">
@@ -4647,10 +4413,8 @@
       <c r="H19" s="5" t="n">
         <v>25.940472</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="5" t="n">
+        <v>37.471417</v>
       </c>
     </row>
     <row r="20">
@@ -4666,7 +4430,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Cash and cash equivalents 3(e)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4679,16 +4443,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>4.794253</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="5" t="n">
         <v>11.052838</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="5" t="n">
+        <v>1.649592</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4699,22 +4463,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4723,13 +4487,15 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-1.931684</v>
+        <v>4.794253</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-2.037228</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-3.668107</v>
+        <v>11.052838</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4740,39 +4506,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>2021.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Share-based payments 9(c)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.275419</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1.450556</v>
+          <t>Consolidated financial statements for the year ended December</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4783,39 +4545,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>settled.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.032175</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0.033023</v>
+          <t>Consolidated financial statements for the year ended December</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -4826,35 +4584,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>reporting period.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on lease liabilities 8</t>
+          <t>Consolidated financial statements for the year ended December</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.027387</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>0.022008</v>
+      <c r="E24" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4865,37 +4623,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on lease liabilities</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.034305</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4906,35 +4668,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on total</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-1.702247</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>-2.196825</v>
+      <c r="F26" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4945,39 +4713,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Non-capital losses available for future</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Non-capital losses available for future periods</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-0.005098</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>0.003133</v>
+      <c r="F27" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4988,39 +4754,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Non-capital losses available for future</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prepaids and deposits</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Non-capital losses available for future total</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.020082</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-0.021892</v>
+      <c r="F28" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -5031,22 +4795,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Unrecognized deferred tax assets                                                    (510,000)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Net deferred tax assets</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>DeferredTaxAssets</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5059,11 +4823,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.001534</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>0.072056</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -5074,39 +4842,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Interest and foreign exchange adjustment on</t>
+          <t>Temporary differences                                        Expiry date</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation assets No expiry date</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-1.728961</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-2.143528</v>
+      <c r="F30" s="5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -5117,17 +4883,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Temporary differences                                        Expiry date</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Exploration and evaluation properties</t>
+          <t>Property and equipment No expiry date</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -5137,13 +4903,17 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-3.827614</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-5.124866</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>-7.149175</v>
+        <v>0.018</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -5154,33 +4924,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-capital losses available for future periods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="5" t="n">
+        <v>0.966</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.110184</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>-0.22713</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>-0.040887</v>
+        <v>0.002042</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -5191,37 +4963,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Brazil                                      No expiry date           731,000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consolidated financial statements for the year ended December</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>6.162475</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-5.351996</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>-7.190062</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5237,35 +5007,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Repayment of lease liabilities 8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>-1.931684</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.075062</v>
+        <v>-2.037228</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-0.072994</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.668107</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-3.675908</v>
       </c>
     </row>
     <row r="35">
@@ -5276,15 +5046,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Common shares issued under private placement 9(b)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Share-based payments 9(c)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5296,17 +5070,13 @@
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>13.697973</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.275419</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1.450556</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.8532920000000001</v>
       </c>
     </row>
     <row r="36">
@@ -5317,15 +5087,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Common shares issue cost 9(b)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Depreciation 7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5337,17 +5111,13 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.317444</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032175</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.033023</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.032172</v>
       </c>
     </row>
     <row r="37">
@@ -5358,12 +5128,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exercise of stock options 9(b)</t>
+          <t>Interest on lease liabilities 8</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -5377,16 +5147,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>0.034075</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.003338</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022008</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.018088</v>
       </c>
     </row>
     <row r="38">
@@ -5397,19 +5167,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net cash (used in)/from financing activities</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Foreign exchange loss/(gain) on lease liabilities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -5420,16 +5186,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>13.339542</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>-0.069656</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.034305</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.016592</v>
       </c>
     </row>
     <row r="39">
@@ -5440,35 +5206,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents during</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Operating activities total</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F39" s="5" t="n">
+        <v>-1.382486</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>6.258585</v>
+        <v>-1.702247</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>-9.403245999999999</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.196825</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-2.755764</v>
       </c>
     </row>
     <row r="40">
@@ -5479,17 +5245,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5498,18 +5264,16 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1e-06</v>
+        <v>-0.025816</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>4.794253</v>
+        <v>-0.005098</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>11.052838</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003133</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>-0.013071</v>
       </c>
     </row>
     <row r="41">
@@ -5520,17 +5284,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
+          <t>Prepaids and deposits</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5539,18 +5303,16 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>4.794253</v>
+        <v>-0.048928</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>11.052838</v>
+        <v>-0.020082</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1.649592</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.021892</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>-0.255684</v>
       </c>
     </row>
     <row r="42">
@@ -5561,33 +5323,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash interest earned</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.042498</v>
+        <v>0.160607</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.150007</v>
+        <v>-0.001534</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.355739</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.072056</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.028488</v>
       </c>
     </row>
     <row r="43">
@@ -5598,17 +5362,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses included in</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses included in accounts payable</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5616,21 +5380,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>-1.296623</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.322114</v>
+        <v>-1.728961</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.789865</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.143528</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>-3.053007</v>
       </c>
     </row>
     <row r="44">
@@ -5641,12 +5401,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capitalized depreciation included in exploration</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Capitalized depreciation included in exploration and evaluation properties 6,7</t>
+          <t>Exploration and evaluation properties</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -5655,21 +5415,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F44" s="5" t="n">
+        <v>-3.827614</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.143478</v>
+        <v>-5.124866</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.159309</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.149175</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-8.339675</v>
       </c>
     </row>
     <row r="45">
@@ -5680,12 +5436,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capitalized share-based payments included in</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Capitalized share-based payments included in exploration and evaluation properties 6</t>
+          <t>Property and equipment</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -5694,21 +5450,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" s="5" t="n">
+        <v>-0.110184</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.096985</v>
+        <v>-0.22713</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.12942</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040887</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.011411</v>
       </c>
     </row>
     <row r="46">
@@ -5719,35 +5471,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capitalized share-based payments included in</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Change in estimate of right-of-use assets</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="5" t="n">
+        <v>6.162475</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.07692300000000001</v>
+        <v>-5.351996</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-0.007219</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.190062</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-8.351086</v>
       </c>
     </row>
     <row r="47">
@@ -5758,12 +5510,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capitalized share-based payments included in</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Additions to right-of-use assets</t>
+          <t>Common shares issued 9(b)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5777,16 +5529,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>0.017754</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>0.051177</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>15.0029</v>
       </c>
     </row>
     <row r="48">
@@ -5797,39 +5551,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Common shares issue cost 9(b)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>0.492632</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.275419</v>
+        <v>-0.317444</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="5" t="n">
+        <v>-1.070741</v>
       </c>
     </row>
     <row r="49">
@@ -5840,39 +5590,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Exercise of stock options 9(b)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>0.024125</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.032175</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.034075</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.003338</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.107568</v>
       </c>
     </row>
     <row r="50">
@@ -5883,12 +5627,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities</t>
+          <t>Repayment of lease liabilities 8</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -5897,21 +5641,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.032441</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.027387</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.075062</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-0.072994</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.082376</v>
       </c>
     </row>
     <row r="51">
@@ -5922,17 +5664,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Net cash provided by/(used in) financing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Operating activities total</t>
+          <t>Net cash provided by/(used in) financing activities</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5940,21 +5682,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>-1.382486</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-1.702247</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>-0.069656</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>13.957351</v>
       </c>
     </row>
     <row r="52">
@@ -5965,17 +5707,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Net cash provided by/(used in) financing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5983,21 +5725,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>-0.025816</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.005098</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-9.403245999999999</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>2.553258</v>
       </c>
     </row>
     <row r="53">
@@ -6008,17 +5750,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Net cash provided by/(used in) financing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prepaids and deposits</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6026,21 +5768,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>-0.048928</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.020082</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>11.052838</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1.649592</v>
       </c>
     </row>
     <row r="54">
@@ -6051,17 +5793,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Net cash provided by/(used in) financing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6069,21 +5811,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.160607</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.001534</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>1.649592</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>4.20285</v>
       </c>
     </row>
     <row r="55">
@@ -6094,39 +5836,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash interest earned</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-1.296623</v>
+        <v>0.042498</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-1.728961</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.150007</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.355739</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.24894</v>
       </c>
     </row>
     <row r="56">
@@ -6137,37 +5871,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Exploration and evaluation expenses included in</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cash received under the Arrangement 1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Exploration and evaluation expenses included in accounts payable</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>10.100273</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.322114</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.789865</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>1.032077</v>
       </c>
     </row>
     <row r="57">
@@ -6178,39 +5912,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Capitalized depreciation included in exploration</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net cash (used in)/from investing activities</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Capitalized depreciation included in exploration and evaluation properties 6,7</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>6.162475</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-5.351996</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.143478</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.159309</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.083957</v>
       </c>
     </row>
     <row r="58">
@@ -6221,12 +5949,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Common shares issued under private</t>
+          <t>Capitalized share-based payments included in</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Common shares issued under private placement 9(b)</t>
+          <t>Capitalized share-based payments included in exploration and evaluation properties 6</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -6241,17 +5969,13 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>13.697973</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.096985</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.12942</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.147806</v>
       </c>
     </row>
     <row r="59">
@@ -6262,12 +5986,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Common shares issued under private</t>
+          <t>Transfer of reserves to capital stock on exercise</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share issue cost 9(b)</t>
+          <t>Transfer of reserves to capital stock on exercise of RSUs and stock options</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -6281,18 +6005,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.317444</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.002526</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.246762</v>
       </c>
     </row>
     <row r="60">
@@ -6303,12 +6025,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Common shares issued under private</t>
+          <t>Transfer of reserves to capital stock on exercise</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Exercise of stock options</t>
+          <t>Change in estimate of right-of-use assets 8</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -6322,13 +6044,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.034075</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>-0.007219</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6344,12 +6066,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Common shares issued under private</t>
+          <t>Transfer of reserves to capital stock on exercise</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Repayment of lease liabilities</t>
+          <t>Additions to right-of-use assets 8</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -6358,16 +6080,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>-0.0716</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.075062</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.051177</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6383,34 +6107,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Common shares issued under private</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Interest and foreign exchange adjustment on lease liabilities 8</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.0716</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>13.339542</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027387</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.022008</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6426,12 +6146,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents during the year</t>
+          <t>Foreign exchange gain on lease liabilities</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6440,16 +6160,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>4.794252</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>6.258585</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>-0.034305</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6465,12 +6187,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cash income taxes earned/(paid)</t>
+          <t>Interest and foreign exchange adjustment on total</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -6484,15 +6206,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G64" s="5" t="n">
+        <v>-1.702247</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>-2.196825</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6508,32 +6226,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Non-cash investing activities</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shares issued under the Arrangement 1,9(b)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>16.441547</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-0.005098</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.003133</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6549,32 +6269,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>included in accounts payable acquired</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>included in accounts payable acquired under the Arrangement 7</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Prepaids and deposits</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>0.529399</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-0.020082</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>-0.021892</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6590,12 +6312,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses included in accounts payable 7</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6608,16 +6330,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>0.330225</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.322114</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001534</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.072056</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6633,30 +6355,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capitalized depreciation included in</t>
+          <t>Interest and foreign exchange adjustment on</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Capitalized depreciation included in exploration and evaluation properties 6,7</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0.054656</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.143478</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.728961</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>-2.143528</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6672,12 +6398,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capitalized stock compensation included</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Capitalized stock compensation included in exploration and evaluation properties 9(c)</t>
+          <t>Common shares issued under private placement 9(b)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6692,7 +6418,7 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.096985</v>
+        <v>13.697973</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -6713,30 +6439,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>on November</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>on November</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash (used in)/from financing activities</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>13.339542</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>-0.069656</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6752,36 +6482,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Change in cash and cash equivalents during</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net loss for the year/period</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-1.931684</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>6.258585</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>-9.403245999999999</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6797,32 +6521,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash and cash equivalents, beginning of</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Repayment of lease liabilities</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.0716</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-06</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>4.794253</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>11.052838</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6838,17 +6562,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash and cash equivalents, beginning of</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Cash and cash equivalents, end of year</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6857,17 +6581,13 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.0716</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.794253</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>11.052838</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>1.649592</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6883,12 +6603,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Capitalized share-based payments included in</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Change in cash during the year/period</t>
+          <t>Change in estimate of right-of-use assets</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -6897,18 +6617,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>4.794252</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>-0.07692300000000001</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-0.007219</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6924,30 +6642,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Capitalized share-based payments included in</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash, beginning of year/period</t>
+          <t>Additions to right-of-use assets</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.017754</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.051177</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6963,25 +6681,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cash, end of year/period</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>1e-06</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>4.794253</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.492632</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.275419</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -7002,29 +6724,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cash income taxes earned (paid)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="5" t="n">
+        <v>0.024125</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.032175</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -7045,12 +6767,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Non-cash investing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Shares issued under the Arrangement 1,10</t>
+          <t>Interest on lease liabilities</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7060,12 +6782,10 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>16.441547</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032441</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.027387</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -7086,20 +6806,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>statements.</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Consolidated financial statements for the year ended December</t>
+          <t>Cash received under the Arrangement 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>0.002022</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>10.100273</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7125,25 +6847,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>THE PERIOD FROM INCORPORATION ON NOVEMBER 25,</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2021 TO DECEMBER</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>0.002021</v>
+          <t>Net cash (used in)/from investing activities</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.162475</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-5.351996</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -7164,25 +6890,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arrangement.</t>
+          <t>Common shares issued under private</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Our shares began trading on the Toronto Venture Exchange (TSXV) on April</t>
+          <t>Common shares issued under private placement 9(b)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>13.697973</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -7203,25 +6931,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>common share of Lavras Gold.</t>
+          <t>Common shares issued under private</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Consolidated financial statements for the year ended December</t>
+          <t>Share issue cost 9(b)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.317444</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -7242,25 +6972,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>favourable terms.</t>
+          <t>Common shares issued under private</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Consolidated financial statements for the year ended December</t>
+          <t>Exercise of stock options</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.034075</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -7276,149 +7008,141 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expense (income)</t>
+          <t>Common shares issued under private</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>General and administrative 12</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Repayment of lease liabilities</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>2.524411</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>2.885462</v>
+      <c r="F84" s="5" t="n">
+        <v>-0.0716</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-0.075062</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Expense (income)</t>
+          <t>Common shares issued under private</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Share-based payments 9(c),11</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>1.450556</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>0.8532920000000001</v>
+      <c r="F85" s="5" t="n">
+        <v>-0.0716</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>13.339542</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Expense (income)</t>
+          <t>Change in cash and cash equivalents</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>0.033023</v>
-      </c>
-      <c r="I86" s="5" t="n">
-        <v>0.032172</v>
+      <c r="F86" s="5" t="n">
+        <v>4.794252</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>6.258585</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Expense (income)</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Foreign exchange loss/(gain)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Cash income taxes earned/(paid)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7434,27 +7158,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H87" s="5" t="n">
-        <v>-0.031065</v>
-      </c>
-      <c r="I87" s="5" t="n">
-        <v>0.109463</v>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Expense (income)</t>
+          <t>Non-cash investing activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Expense (income) total</t>
+          <t>Shares issued under the Arrangement 1,9(b)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -7463,119 +7191,123 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>16.441547</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H88" s="5" t="n">
-        <v>3.976925</v>
-      </c>
-      <c r="I88" s="5" t="n">
-        <v>3.880389</v>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>included in accounts payable acquired</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>included in accounts payable acquired under the Arrangement 7</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>0.529399</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H89" s="5" t="n">
-        <v>0.355739</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>0.24894</v>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Exploration and evaluation expenses</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Interest and finance charges</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Exploration and evaluation expenses included in accounts payable 7</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>-0.046921</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-0.044459</v>
+      <c r="F90" s="5" t="n">
+        <v>0.330225</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.322114</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Capitalized depreciation included in</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Other income (expense) total</t>
+          <t>Capitalized depreciation included in exploration and evaluation properties 6,7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7584,44 +7316,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0.308818</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>0.204481</v>
+      <c r="F91" s="5" t="n">
+        <v>0.054656</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.143478</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Capitalized stock compensation included</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Capitalized stock compensation included in exploration and evaluation properties 9(c)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -7632,128 +7360,138 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-3.668107</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>-3.675908</v>
+      <c r="G92" s="5" t="n">
+        <v>0.096985</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>on November</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 10</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>on November</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding –</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted 10</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>1e-06</v>
+          <t>Net loss for the year/period</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>30.968669</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>43.757003</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>51.357166</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>57.637812</v>
+        <v>-1.931684</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>General and administrative 12</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Repayment of lease liabilities</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>1.378302</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>1.808557</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>2.524411</v>
+        <v>-0.0716</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7764,35 +7502,41 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Share-based payments 9(c),11</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0.275419</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>1.450556</v>
+      <c r="F96" s="5" t="n">
+        <v>-0.0716</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7803,37 +7547,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Change in cash during the year/period</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.024125</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>0.032175</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>0.033023</v>
+        <v>4.794252</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7844,39 +7588,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.017076</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>-0.031065</v>
+          <t>Cash, beginning of year/period</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7887,33 +7627,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Expenses (income) total</t>
+          <t>Cash, end of year/period</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>1.931684</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>2.099075</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>3.976925</v>
+        <v>4.794253</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7924,24 +7666,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Cash income taxes earned (paid)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -7952,11 +7690,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" s="5" t="n">
-        <v>0.150007</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0.355739</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7967,17 +7709,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Non-cash investing activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Interest and finance charges</t>
+          <t>Shares issued under the Arrangement 1,10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7986,16 +7728,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>-0.08816</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>-0.046921</v>
+      <c r="F101" s="5" t="n">
+        <v>16.441547</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -8006,39 +7750,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>statements.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.061847</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.308818</v>
+          <t>Consolidated financial statements for the year ended December</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8049,39 +7789,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>THE PERIOD FROM INCORPORATION ON NOVEMBER 25,</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>-2.037228</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>-3.668107</v>
+          <t>2021 TO DECEMBER</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -8092,39 +7828,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Arrangement.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 10</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>-7e-08</v>
+          <t>Our shares began trading on the Toronto Venture Exchange (TSXV) on April</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8135,30 +7867,30 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>common share of Lavras Gold.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9(c), 11</t>
+          <t>Consolidated financial statements for the year ended December</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.492632</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.275419</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -8174,34 +7906,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>favourable terms.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain)/loss</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consolidated financial statements for the year ended December</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.034651</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>-0.017076</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -8222,17 +7950,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expense (income)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>General and administrative 12</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8240,21 +7968,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>-0.042498</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>-0.150007</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>2.524411</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>2.885462</v>
       </c>
     </row>
     <row r="108">
@@ -8265,12 +7993,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expense (income)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Interest and finance charges</t>
+          <t>Share-based payments 9(c),11</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8279,21 +8007,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>0.044472</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>0.08816</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>1.450556</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0.8532920000000001</v>
       </c>
     </row>
     <row r="109">
@@ -8304,17 +8032,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expense (income)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8322,21 +8050,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="5" t="n">
-        <v>-1.931684</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>-2.037228</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.033023</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.032172</v>
       </c>
     </row>
     <row r="110">
@@ -8347,15 +8075,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expense (income)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Deferred tax (expense)/recovery 13</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Foreign exchange loss/(gain)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -8371,15 +8103,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H110" s="5" t="n">
+        <v>-0.031065</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.109463</v>
       </c>
     </row>
     <row r="111">
@@ -8390,39 +8118,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expense (income)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Total loss and comprehensive loss 10</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Expense (income) total</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>-1.931684</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>-2.037228</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>3.976925</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>3.880389</v>
       </c>
     </row>
     <row r="112">
@@ -8433,17 +8157,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 10</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8451,21 +8175,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.355739</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0.24894</v>
       </c>
     </row>
     <row r="113">
@@ -8476,35 +8200,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>on November</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Notes 31, 2022</t>
+          <t>Interest and finance charges</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>-0.046921</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>-0.044459</v>
       </c>
     </row>
     <row r="114">
@@ -8515,41 +8239,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Other income (expense) total</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>0.034651</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H114" s="5" t="n">
+        <v>0.308818</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0.204481</v>
       </c>
     </row>
     <row r="115">
@@ -8560,15 +8278,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Deferred tax (expense) recovery</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -8584,15 +8306,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>-3.668107</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>-3.675908</v>
       </c>
     </row>
     <row r="116">
@@ -8603,32 +8321,983 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 10</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding –</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding – basic and diluted 10</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>30.968669</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>43.757003</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>51.357166</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>57.637812</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>General and administrative 12</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>1.378302</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.808557</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>2.524411</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Share-based payments 9(c),11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.275419</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>1.450556</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.024125</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.032175</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.033023</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-0.017076</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-0.031065</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Expenses (income) total</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>1.931684</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>2.099075</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>3.976925</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.150007</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.355739</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Interest and finance charges</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.08816</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>-0.046921</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Other income (expenses) total</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.061847</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0.308818</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>-2.037228</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-3.668107</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 10</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 9(c), 11</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.492632</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.275419</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Foreign exchange (gain)/loss</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.034651</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-0.017076</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-0.042498</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-0.150007</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Interest and finance charges</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.044472</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.08816</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>-1.931684</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>-2.037228</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Deferred tax (expense)/recovery 13</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Total loss and comprehensive loss 10</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>-1.931684</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>-2.037228</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 10</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>on November</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Notes 31, 2022</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0.034651</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Deferred tax (expense) recovery</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>statements.</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Consolidated financial statements for the year ended December</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
         <v>0.002022</v>
       </c>
-      <c r="F116" s="5" t="n">
+      <c r="F139" s="5" t="n">
         <v>3.1e-05</v>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
